--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -110,13 +110,13 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>761721f0-1260-4d2a-9bbf-efce45c21956</x:t>
+    <x:t>2026-06-18T13:59:11.7836354Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2026-06-18T13:44:49.0239945Z</x:t>
+    <x:t>6573c6cc-c72b-4671-9c58-5ce486bf46d5</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -629,7 +629,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>32</x:v>
@@ -638,7 +638,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -110,13 +110,13 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-18T13:59:11.7836354Z</x:t>
+    <x:t>2026-06-18T14:05:14.9567265Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>6573c6cc-c72b-4671-9c58-5ce486bf46d5</x:t>
+    <x:t>5adc0c0c-991d-4652-9041-c1fa405cc1de</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -110,13 +110,19 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-18T14:05:14.9567265Z</x:t>
+    <x:t>2026-06-18T14:17:38.1196598Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>5adc0c0c-991d-4652-9041-c1fa405cc1de</x:t>
+    <x:t>46867269-f480-49b0-9459-06a9586250fc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-18T14:17:29.9468992Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cf434bdf-d651-4921-91cd-d8e52abd1564</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -629,7 +635,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>32</x:v>
@@ -639,6 +645,23 @@
       </x:c>
       <x:c r="E2" s="0" t="s">
         <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>34</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -110,7 +110,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-18T14:17:38.1196598Z</x:t>
+    <x:t>2026-06-18T14:36:05.1322370Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -119,10 +119,10 @@
     <x:t>46867269-f480-49b0-9459-06a9586250fc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-18T14:17:29.9468992Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cf434bdf-d651-4921-91cd-d8e52abd1564</x:t>
+    <x:t>2026-06-18T14:35:56.7498070Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>b6fde1b0-cf2b-49e4-b1fb-9579dd54ddcc</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -110,7 +110,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-18T14:36:05.1322370Z</x:t>
+    <x:t>2026-06-19T13:23:40.3068377Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -119,10 +119,10 @@
     <x:t>46867269-f480-49b0-9459-06a9586250fc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-18T14:35:56.7498070Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>b6fde1b0-cf2b-49e4-b1fb-9579dd54ddcc</x:t>
+    <x:t>2026-06-19T13:23:31.7868130Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>e15bc970-dcde-4dac-a8f0-a1341fac7e52</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -110,7 +110,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-19T13:23:40.3068377Z</x:t>
+    <x:t>2026-07-03T19:54:32.2687591Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -119,10 +119,10 @@
     <x:t>46867269-f480-49b0-9459-06a9586250fc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-19T13:23:31.7868130Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>e15bc970-dcde-4dac-a8f0-a1341fac7e52</x:t>
+    <x:t>2026-06-30T14:25:18.5779134Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ccda5a4c-d28f-445f-b35d-ed4f22896014</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -1,16 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:workbook xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
+    <x:workbookView windowWidth="21216" windowHeight="8964" firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Endpoints" sheetId="1" r:id="rId2"/>
-    <x:sheet name="Endpoint_Response" sheetId="2" r:id="rId3"/>
+    <x:sheet name="Endpoints" sheetId="1" r:id="rId1"/>
+    <x:sheet name="Endpoint_Response" sheetId="2" r:id="rId2"/>
   </x:sheets>
   <x:definedNames/>
-  <x:calcPr calcId="125725"/>
+  <x:calcPr calcId="191029"/>
+  <x:extLst>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </x:ext>
+  </x:extLst>
 </x:workbook>
 </file>
 
@@ -80,7 +94,64 @@
     <x:t>id</x:t>
   </x:si>
   <x:si>
-    <x:t>aca81f11-4fed-4eb1-8ffa-786a7c8a68eb</x:t>
+    <x:t>getPACFByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetPACFByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>getCompanyContactListByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetCompanyContactListByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>getPACFInspectionByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetPACFInspectionByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>getPACFStaffByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetPACFStaffByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>getPACFResidentCareByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetPACFResidentCareByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>getPACFPatientCareByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetPACFPatientCareByBusinessUnitID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>toggleBusinessUnitVisibility</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/ToggleBusinessUnitVisibility</x:t>
+  </x:si>
+  <x:si>
+    <x:t>getPACFListByKeyWord</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetPACFListByKeyWord</x:t>
+  </x:si>
+  <x:si>
+    <x:t>getPACFList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/GetPACFList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>addOrUpdateCompanyHospital</x:t>
+  </x:si>
+  <x:si>
+    <x:t>api/BusinessUnit/AddOrUpdateCompanyHospital</x:t>
   </x:si>
   <x:si>
     <x:t>create_product</x:t>
@@ -92,15 +163,9 @@
     <x:t>CacheId</x:t>
   </x:si>
   <x:si>
-    <x:t>0e37b17e-09b7-4a73-8ff1-d0a2704256cd</x:t>
-  </x:si>
-  <x:si>
     <x:t>MemberId</x:t>
   </x:si>
   <x:si>
-    <x:t>Success! Member information added. MemberId:63c414ed-333d-4bb4-8ff9-03f4a09df5f1, BusinessunitMemberId:d48a486d-25ec-448b-bb54-953570acbf00</x:t>
-  </x:si>
-  <x:si>
     <x:t>HttpStatus</x:t>
   </x:si>
   <x:si>
@@ -110,7 +175,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-07-03T19:54:32.2687591Z</x:t>
+    <x:t>2026-07-09T20:08:09.8145542Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -119,20 +184,180 @@
     <x:t>46867269-f480-49b0-9459-06a9586250fc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-06-30T14:25:18.5779134Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ccda5a4c-d28f-445f-b35d-ed4f22896014</x:t>
+    <x:t>2026-07-06T07:47:11.1535627Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23ebc7e9-2cbd-45b1-a86f-80d059455b95</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="0" formatCode=""/>
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr9">
+  <x:numFmts count="4">
+    <x:numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <x:numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <x:numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <x:numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="22">
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:charset val="134"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:charset val="134"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:u/>
+      <x:sz val="11"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:u/>
+      <x:sz val="11"/>
+      <x:color rgb="FF800080"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFF0000"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color theme="3"/>
+      <x:name val="Calibri"/>
+      <x:charset val="134"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="11"/>
+      <x:color rgb="FF7F7F7F"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="15"/>
+      <x:color theme="3"/>
+      <x:name val="Calibri"/>
+      <x:charset val="134"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="13"/>
+      <x:color theme="3"/>
+      <x:name val="Calibri"/>
+      <x:charset val="134"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="3"/>
+      <x:name val="Calibri"/>
+      <x:charset val="134"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF3F3F76"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF3F3F3F"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFA7D00"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FFFA7D00"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF006100"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C0006"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF9C6500"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="0"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Calibri"/>
+      <x:charset val="0"/>
+      <x:scheme val="minor"/>
+    </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -141,47 +366,537 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="33">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFCC"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFCC99"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFA5A5A5"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC6EFCE"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFC7CE"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFEB9C"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0.799981688894314"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0.599993896298105"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="4" tint="0.399975585192419"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.799981688894314"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.599993896298105"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="5" tint="0.399975585192419"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="6"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="6" tint="0.799981688894314"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="6" tint="0.599993896298105"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="6" tint="0.399975585192419"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="7"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="7" tint="0.799981688894314"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="7" tint="0.599993896298105"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="7" tint="0.399975585192419"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="8"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="8" tint="0.799981688894314"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="8" tint="0.599993896298105"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="8" tint="0.399975585192419"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="9"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="9" tint="0.799981688894314"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="9" tint="0.599993896298105"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor theme="9" tint="0.399975585192419"/>
+        <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="1">
-    <x:border diagonalUp="0" diagonalDown="0">
-      <x:left style="none">
-        <x:color rgb="FF000000"/>
+  <x:borders count="9">
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB2B2B2"/>
       </x:left>
-      <x:right style="none">
-        <x:color rgb="FF000000"/>
+      <x:right style="thin">
+        <x:color rgb="FFB2B2B2"/>
       </x:right>
-      <x:top style="none">
-        <x:color rgb="FF000000"/>
+      <x:top style="thin">
+        <x:color rgb="FFB2B2B2"/>
       </x:top>
-      <x:bottom style="none">
-        <x:color rgb="FF000000"/>
+      <x:bottom style="thin">
+        <x:color rgb="FFB2B2B2"/>
       </x:bottom>
-      <x:diagonal style="none">
-        <x:color rgb="FF000000"/>
-      </x:diagonal>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="medium">
+        <x:color theme="4"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="medium">
+        <x:color theme="4" tint="0.499984740745262"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF7F7F7F"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF3F3F3F"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF3F3F3F"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF3F3F3F"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF3F3F3F"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left style="double">
+        <x:color rgb="FF3F3F3F"/>
+      </x:left>
+      <x:right style="double">
+        <x:color rgb="FF3F3F3F"/>
+      </x:right>
+      <x:top style="double">
+        <x:color rgb="FF3F3F3F"/>
+      </x:top>
+      <x:bottom style="double">
+        <x:color rgb="FF3F3F3F"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom style="double">
+        <x:color rgb="FFFF8001"/>
+      </x:bottom>
+      <x:diagonal/>
+    </x:border>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top style="thin">
+        <x:color theme="4"/>
+      </x:top>
+      <x:bottom style="double">
+        <x:color theme="4"/>
+      </x:bottom>
+      <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
+  <x:cellStyleXfs count="49">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
+    <x:xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
+  <x:cellXfs count="2">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </x:cellXfs>
-  <x:cellStyles count="1">
+  <x:cellStyles count="49">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <x:cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <x:cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <x:cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <x:cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <x:cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <x:cellStyle name="Link" xfId="6" builtinId="8"/>
+    <x:cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <x:cellStyle name="Note" xfId="8" builtinId="10"/>
+    <x:cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <x:cellStyle name="Title" xfId="10" builtinId="15"/>
+    <x:cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <x:cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <x:cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <x:cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <x:cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <x:cellStyle name="Input" xfId="16" builtinId="20"/>
+    <x:cellStyle name="Output" xfId="17" builtinId="21"/>
+    <x:cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <x:cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <x:cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <x:cellStyle name="Total" xfId="21" builtinId="25"/>
+    <x:cellStyle name="Good" xfId="22" builtinId="26"/>
+    <x:cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <x:cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <x:cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <x:cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <x:cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <x:cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <x:cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <x:cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <x:cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <x:cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <x:cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <x:cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <x:cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <x:cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <x:cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <x:cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <x:cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <x:cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <x:cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <x:cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <x:cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <x:cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <x:cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <x:cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <x:cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <x:cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </x:cellStyles>
+  <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <x:tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <x:tableStyleElement type="wholeTable" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" dxfId="2"/>
+      <x:tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </x:tableStyle>
+    <x:tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <x:tableStyleElement type="headerRow" dxfId="16"/>
+      <x:tableStyleElement type="totalRow" dxfId="15"/>
+      <x:tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <x:tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <x:tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <x:tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <x:tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <x:tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <x:tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <x:tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </x:tableStyle>
+  </x:tableStyles>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </x:ext>
+  </x:extLst>
 </x:styleSheet>
 </file>
 
@@ -464,17 +1179,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B15"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:dimension ref="A1:G25"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="14.4"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38.444444" style="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="0" t="s">
@@ -568,50 +1285,121 @@
       <x:c r="A12" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B15" s="0" t="s">
+    </x:row>
+    <x:row r="16" spans="1:2">
+      <x:c r="A16" s="0" t="s">
         <x:v>27</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:2">
+      <x:c r="A17" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:2">
+      <x:c r="A18" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:2">
+      <x:c r="A19" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:2">
+      <x:c r="A20" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:2">
+      <x:c r="A21" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:2">
+      <x:c r="A22" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:2">
+      <x:c r="A23" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:2">
+      <x:c r="A24" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:2">
+      <x:c r="A25" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:dimension ref="A1:E3"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="14.4"/>
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
@@ -621,53 +1409,53 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -175,7 +175,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-07-09T20:08:09.8145542Z</x:t>
+    <x:t>2026-07-13T13:15:17.4891791Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -184,10 +184,10 @@
     <x:t>46867269-f480-49b0-9459-06a9586250fc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-07-06T07:47:11.1535627Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23ebc7e9-2cbd-45b1-a86f-80d059455b95</x:t>
+    <x:t>2026-07-13T13:15:01.2608410Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>f4d7f350-1dec-4934-873e-2f8a319877a2</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -175,7 +175,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-07-13T13:15:17.4891791Z</x:t>
+    <x:t>2026-07-14T11:40:35.9932539Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -187,7 +187,7 @@
     <x:t>2026-07-13T13:15:01.2608410Z</x:t>
   </x:si>
   <x:si>
-    <x:t>f4d7f350-1dec-4934-873e-2f8a319877a2</x:t>
+    <x:t>cbc3a3c8-e49e-4394-8cf2-7784fa6e22d3</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView windowWidth="21216" windowHeight="8964" firstSheet="0" activeTab="0"/>
+    <x:workbookView windowWidth="28800" windowHeight="12180" firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Endpoints" sheetId="1" r:id="rId1"/>
@@ -97,7 +97,7 @@
     <x:t>getPACFByBusinessUnitID</x:t>
   </x:si>
   <x:si>
-    <x:t>api/BusinessUnit/GetPACFByBusinessUnitID</x:t>
+    <x:t>api/BusinessUnit/GetPACFByBusinessUnitID?PACFBusinessUnitID={PACFBusinessUnitID}</x:t>
   </x:si>
   <x:si>
     <x:t>getCompanyContactListByBusinessUnitID</x:t>
@@ -175,19 +175,85 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-07-14T11:40:35.9932539Z</x:t>
+    <x:t>74befd8a-df40-42c5-9ba1-8724493b7737</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>46867269-f480-49b0-9459-06a9586250fc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-07-13T13:15:01.2608410Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cbc3a3c8-e49e-4394-8cf2-7784fa6e22d3</x:t>
+    <x:t>2026-08-03T13:41:43.8163139Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:43.7151643Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>login</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HospitalRole</x:t>
+  </x:si>
+  <x:si>
+    <x:t>200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzg1NzY4MTAyLCJuYmYiOjE3ODU3NjQ1MDIsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzg1NzY0NTAyfQ.E6DdyRF-S3CGQ6QgrKOyOGdhEJGMXm5otgOkGLheIHEATQa5LYHPtAY00CwKz_xJ2apJka664zmjHMeVvAtGbJVQAtjZ0S5QDB1TS87lc04FosXtHQwgKcCQ7Z-hx93V1rAyrKUXz1mp3LVk03Po-H3Q_2Dker_wMPKX3Pu9jkq0vYsJj_x1Fq8bShktkshO0W5AEBw6lOYFL3gp71owaXcU8-9rLVHsVbLhSSFdY0uczuIEM2Snmv55i7RpiQ4vvNB6TizQ7osV4SWnsx_KJKCbbZ75cq7t40nhCz_swo0Ebk3xUE__w29MzD-Ip_qr84VzDA47cjXGnJFJGEvapQ","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:42.7266947Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Pacf","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":3,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":15,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":100,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":168,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"E","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":false,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"City","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["ServiceInitiated","ShowCLRAReport","ShowReports","SendReferral","ReceiveReferral","PreferredProviderList","SurveyModule","PendingServiceInitiationReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToHighNeed","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForHiCom","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromHighNeed","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareHiCom","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"74befd8a-df40-42c5-9ba1-8724493b7737","AcceptedPolicyIds":[],"LoginError":[]}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:43.6869998Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UserName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hospital@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:43.7328024Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EmailId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:43.7496754Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BusinessUnitId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:43.7659226Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CompanyBusinessUnitId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:43.7849097Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BusinessUnitMemberId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:41:43.8007394Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-03T13:44:17.9801146Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -814,9 +880,8 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -869,28 +934,9 @@
     <x:cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <x:cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </x:cellStyles>
-  <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <x:tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <x:tableStyleElement type="wholeTable" dxfId="6"/>
-      <x:tableStyleElement type="headerRow" dxfId="5"/>
-      <x:tableStyleElement type="totalRow" dxfId="4"/>
-      <x:tableStyleElement type="firstColumn" dxfId="3"/>
-      <x:tableStyleElement type="lastColumn" dxfId="2"/>
-      <x:tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <x:tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </x:tableStyle>
-    <x:tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <x:tableStyleElement type="headerRow" dxfId="16"/>
-      <x:tableStyleElement type="totalRow" dxfId="15"/>
-      <x:tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <x:tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <x:tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <x:tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <x:tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <x:tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <x:tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <x:tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </x:tableStyle>
+  <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
+    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{D26516E5-55CF-4383-B99C-4744BEC979F1}"/>
+    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{8889AFAF-0F25-43FB-AD63-19BD239EB8B4}"/>
   </x:tableStyles>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1187,10 +1233,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G25"/>
-  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="14.4"/>
+  <x:dimension ref="A1:B25"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38.444444" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="38.447619" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="117.571429" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
@@ -1399,7 +1446,7 @@
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1:E3"/>
-  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="14.4"/>
+  <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
@@ -1423,7 +1470,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
         <x:v>49</x:v>
@@ -1432,7 +1479,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1440,7 +1487,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>49</x:v>
@@ -1449,7 +1496,143 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="A8" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="A9" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="A10" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5">
+      <x:c r="A11" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>74</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/TestData/UploadFiles/RequestEndPoint.xlsx
+++ b/TestData/UploadFiles/RequestEndPoint.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView windowWidth="28800" windowHeight="12180" firstSheet="0" activeTab="0"/>
+    <x:workbookView windowWidth="8775" windowHeight="3255" firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Endpoints" sheetId="1" r:id="rId1"/>
@@ -175,19 +175,16 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>74befd8a-df40-42c5-9ba1-8724493b7737</x:t>
+    <x:t>2026-08-08T10:26:05.7952418Z</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>2026-08-03T13:41:43.8163139Z</x:t>
-  </x:si>
-  <x:si>
     <x:t>9eb45736-827a-4751-9996-44088587006e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-03T13:41:43.7151643Z</x:t>
+    <x:t>2026-08-08T10:26:05.7501164Z</x:t>
   </x:si>
   <x:si>
     <x:t>login</x:t>
@@ -199,16 +196,19 @@
     <x:t>200</x:t>
   </x:si>
   <x:si>
-    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzg1NzY4MTAyLCJuYmYiOjE3ODU3NjQ1MDIsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzg1NzY0NTAyfQ.E6DdyRF-S3CGQ6QgrKOyOGdhEJGMXm5otgOkGLheIHEATQa5LYHPtAY00CwKz_xJ2apJka664zmjHMeVvAtGbJVQAtjZ0S5QDB1TS87lc04FosXtHQwgKcCQ7Z-hx93V1rAyrKUXz1mp3LVk03Po-H3Q_2Dker_wMPKX3Pu9jkq0vYsJj_x1Fq8bShktkshO0W5AEBw6lOYFL3gp71owaXcU8-9rLVHsVbLhSSFdY0uczuIEM2Snmv55i7RpiQ4vvNB6TizQ7osV4SWnsx_KJKCbbZ75cq7t40nhCz_swo0Ebk3xUE__w29MzD-Ip_qr84VzDA47cjXGnJFJGEvapQ","token_type":"Bearer","expires_in":"3600"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-03T13:41:42.7266947Z</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Pacf","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":3,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":15,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":100,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":168,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"E","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":false,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"City","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["ServiceInitiated","ShowCLRAReport","ShowReports","SendReferral","ReceiveReferral","PreferredProviderList","SurveyModule","PendingServiceInitiationReminder"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToHighNeed","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForHiCom","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromHighNeed","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareHiCom","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"74befd8a-df40-42c5-9ba1-8724493b7737","AcceptedPolicyIds":[],"LoginError":[]}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-03T13:41:43.6869998Z</x:t>
+    <x:t>{"access_token":"eyJhbGciOiJSUzI1NiIsImtpZCI6Ilg1ZVhrNHh5b2pORnVtMWtsMll0djhkbE5QNC1jNTdkTzZRR1RWQndhTmsiLCJ0eXAiOiJKV1QifQ.eyJhdWQiOiJjOTdhMGNjOC05MTIzLTQxMDgtYTljMS03ZDliZDJhNmI4YzAiLCJpc3MiOiJodHRwczovL3Rlc3Ryb3ZpY2FyZS5iMmNsb2dpbi5jb20vZjFmMGRmYzctM2EzYy00ZWMyLWIwOWMtNTRlZWQ4NGMyMGYxL3YyLjAvIiwiZXhwIjoxNzg2MTg4MzY0LCJuYmYiOjE3ODYxODQ3NjQsImlkcCI6IkxvY2FsQWNjb3VudCIsInN1YiI6IjA2M2E5YmY2LWNhOGItNGMxZi1hMGZiLTQ5OGY3YjIwMjBmYiIsImVtYWlscyI6WyJob3NwaXRhbEByb3ZpY2FyZS5jb20iXSwidGZwIjoiQjJDXzFfUk9QQ19UZXN0Iiwic2NwIjoiV2ViQ2xpZW50IiwiYXpwIjoiYzZhYmM1NjctM2Y0YS00YjEzLTg1OTMtNzY0YjIwOWExN2VhIiwidmVyIjoiMS4wIiwiaWF0IjoxNzg2MTg0NzY0fQ.UYv8cJshwXXOCtQSWUYi6zF5nZ42QmrngmfdA95NguCE5z6RKIBa5opJsAqv_0hhC43NjjgfZ8i1_Ie92jPpOOc4AdlDU-fSQzR17wZXWGcLT8DJ7XhtY7Ir9AOioP3JxBTbI4pWHKw1kb_IJNkEksk0WLm-73chda-q9mfQOrU16DZdnaibmC3bg5x8__L6ScfCDC4mlxD63oHy3lnwoxjaU9gflgmdYa_qDxDsa7MPKOQCPkeQ7x0cc8iPnGEwSfVU6ifYeCL90vmVJ4zSOiEwL4Eybdkx1h7Y8Uc8UW_7u_NAeFSU1aTyMJFUW8xa_lMJwol0dv6IwV2EAuef0w","token_type":"Bearer","expires_in":"3600"}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:26:04.8778136Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1f61822b-0b4c-4162-82e8-c8a711d92c13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"MemberId":"9eb45736-827a-4751-9996-44088587006e","FirstName":"Arizona","LastName":"Rovicare ","UserName":"hospital@rovicare.com","EmailId":"hospital@rovicare.com","BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","CompanyBusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","BusinessUnitName":"Arizona State Hospital","BusinessUnitType":"Pacf","AssignedSettings":{"ReferralVisibilityInHrs":120,"ExtendedReferralVisibilityInHrs":192,"RatingReminderInDays":2,"ReferralViewDelayInMins":30,"IsEnableOrphanReferral":true,"IsEnable2StepAppointment":false,"AllowMemberAssigntoReferralForSendReferral":true,"AllowMemberViewAllReferralForSendReferral":true,"AllowMemberAssigntoReferralForReceiveReferral":false,"AllowMemberViewAllReferralForReceiveReferral":true,"DefaultHealthFacilityRating":3,"DefaultMedicareRating":4,"ReferralWithPatientPreferenceNote":null,"SearchAreaBy":"County","MaxSavedSearchAllowed":15,"IsContractSearched":false,"IsFaxReferralActive":true,"IsEmailReferralActive":true,"HadReferralWithAdvanceNotice":true,"WorkStartTime":null,"WorkEndTime":null,"MaxNumberOfOrganizationMembers":50,"MaxNumberOfImagesUploaded":10,"MaxSizeOfImagesUploadedInMB":50,"DurationOfHistoricalRecordsInDays":120,"LastSynOn":"2023-11-22T12:45:57.1111937Z","DefaultProviderType":null,"PatientVisibilityDays":30,"ConfirmReferralVisibilityInHrs":168,"LoginMethod":"Rovicare","DefaultFilter":"Medical","ShowInsurance":"Outgoing","IsTwelveTimeFormat":false,"ReceiveReferralDeliveryMode":"ES","SendReferralToMemberViaFax":false,"EmrType":"Rovicare","EditRecordImportPatient":false,"AddRecordImportPatient":false,"OverrideRecordImportPatient":false,"AutomaticOverrideRecordImportPatient":true,"IsFullCapacity":true,"AcceptReferral":true,"IndicateToOrigin":true,"InpatientReferralActive":null,"OutpatientReferralActive":null,"PreAuthorizationRequired":false,"SharePatientRecord":false,"UpdateReferralResponse":true,"AutomaticallySharePatientRecord":false,"TentativeAcceptPatient":false,"ShowAverageResponseRate":false,"ResponseRateBusinessunitIds":"","DestinationCaseManagerConfig":"Email,Name,WorkNumber","CaseManagerDetailsConfig":"PhoneNumber,Email","DefaultShortlistPaginationCount":"50","DelayedClinicalRecordDays":null,"FaxNumberToSendCocDocument":null,"FollowUpRemovalTimeInMinutes":43200,"CocDocumentRequiringInsuranceList":[],"FollowUp7DayReminderTimeInMinute":10080,"FollowUp30DayReminderTimeInMinute":43200,"InpatientVisitReminderTimeInMinute":1440,"HiCommNotificationReminderInMinute":1440,"HiCommIPVDueDateOffsetDays":7,"CocDocumentReminderTimeInMinute":4320,"ShowAhcccsInfo":false,"UpdateCampus":false,"HiCommPatientReadmitIntervalInDays":30,"LocalTimeZoneId":null,"AssignPatientTagToHiCoM":null,"TeamAssignmentNotification":true,"WorkingDays":[{"Day":"Mon","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Tue","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Wed","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Thu","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Fri","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Sat","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false},{"Day":"Sun","IsFullDay":false,"IsEnabled":false,"StartTime":"9am","EndTime":"8pm","IsAdded":false}],"Insurance":[],"CareRequirement":[],"ProviderType":[],"ServiceSetting":[],"SpecialProgram":[],"AgeGroup":[],"GenderType":[],"FacilityType":[],"AppointmentStatus":[],"FollowUpStatus":[],"DefaultRoute":null,"ConfigurableLogo":null,"Theme":null,"EnableDmeNotification":false,"WorkspaceConfigurations":[]},"DmeSettings":{"HcpNotificationMode":null,"EnableWoundCareQuantity":false,"EnableHhaCosmetics":false,"AllowShipToClinicianHome":false,"ShowEpisodeNumber":false},"EMRSetting":"{\"emrType\":\"Rovicare\",\"organizationName\":\"string\",\"organizationId\":\"string\",\"facilityId\":\"string\",\"AdvancedMdProgressNoteDateChanged\":\"string\",\"facilityUTCOffsetValue\":0.0,\"facilityAddress\":{\"streetAddress\":\"string\",\"city\":\"string\",\"state\":\"string\",\"zipcode\":\"string\"},\"providerType\":\"string\",\"facilityContact\":\"string\",\"healthCareResources\":{\"AllergyIntolerances\":true,\"Conditions\":true,\"Coverage\":true,\"DiagnosticReports\":true,\"Immunizations\":true,\"Medications\":true,\"ProgressNotes\":true,\"EmergencyContacts\":true,\"CarePlans\":true},\"MedicalRecordAccessLevel\":\"string\",\"HieFileInfo\":{\"BlobPathList\":[\"string\"],\"FileDirectoryFromUser\":\"string\",\"AddPatientIfNotExists\":true},\"siteId\":\"string\",\"fTPClientSettingModel\":{\"Host\":\"string\",\"Port\":0,\"UserName\":\"string\",\"Password\":\"string\",\"FileLocation\":\"string\",\"FileType\":\"string\"},\"EntityUpdates\":[{\"Entity\":\"string\",\"EntityLastUpdateTime\":\"2026-02-16T13:09:58.447Z\"}],\"EntityMetaData\":[{\"Entity\":\"string\",\"SearchParamters\":[{\"Key\":\"string\",\"Value\":\"string\"}]}]}","ServiceArea":"ZipCode","RoleName":"Organization Admin","HasAcceptedLicense":true,"AssignedFeatures":["ImportPatientByExcelsheet","ServiceInitiated","AutomatedOriginStarRating","PartialReferralConfirmation","ReferralHistoryDashboard","HighNeedPatient","RejectionReasonInReferral","RecordReferralForOrigin","ShowCLRAReport","ShowReports","SendReferral","ShareReferrals","ReceiveReferral","NotificationFeature","PreferredProviderList","LiveChat","RecordReferral","GlobalChat","SurveyModule","PendingServiceInitiationReminder","PendingReferralResponseReminder","PreferredProviderAvailability"],"BusinessUnitMemberId":"5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e","PermissionList":["AcceptOrder","AddAppointment","AddAppointmentSlot","AddOrder","AddOrganization","AddOrganizationMember","AddPatient","AddPatientToHighNeed","AddPreferredProvider","AddReferral","AddTag","AdminViewReports","AssignMember","AutoSyncOnAction","AutoSyncOnReferral","BulkActionForHiCom","CancelOrder","CancelReferral","CompulsaryServicesAndSpecialProgram","ConfirmPartialReferral","DeleteAppointment","DeleteAppointmentSlot","DeleteOrganizationMember","DeletePatient","DeletePreferredProvider","DeleteTag","DisableAutoConfirmReferral","DisableReferral","DisableReferralForServices","EditAppointment","EditAppointmentSlot","EditOrder","EditOrganization","EditOrganizationMember","EditPatient","EditPreferredProvider","EditReferral","EditTag","EnableMedicareRating","FaceSheetInMedicalRecords","GlobalChat","ImportPatientByCCDA","ImportPatientByExcelSheet","ImportPatientByFaceSheet","InsuranceProvider","LiveChat","ManageAllOrganization","ManageCompulsoryInsuranceForPatient","ManageCompulsoryServicesAndSpecialProgram","ManageOrganization","MemberAssignedToReferralForReceiveReferral","MessageBoard","MobileApplication","MovePatientToFollowUp","Notes","Notification","OnCallSupport","Order.Bulk.Download","Order.Bulk.Upload","Order.Bulk.View","Order.Document.Download","Order.Sign.Bypass","Order.Sign.OnBehalf","Order.Sign.Remind","Order.Workflow.Decline","Order.Workflow.Disposition","Order.Workflow.TakeOwnership","PatientPreference","PendingReferralsNotification","Prescriber.Search","ProvideRejectionReasonForReferral","ReceiveMedicalRecords","ReceiveReferral","ReceiveReferralSetting","ReferOrder","ReferralReport","ReferralTimeline","RejectOrder","RemovePatientFromHighNeed","ResendReferral","ResponseReferral","ScheduleTransport","SendMedicalRecords","SendReferral","ShareHiCom","ShareMedicalRecords","ShareReferrals","ShareReferralsWithPreferredProviders","ShipOrder","ShowSpecialProgramNeeded","SuperAdmin","Track","UpdatePatientTask","UploadMedicalRecord","ViewAndManageCustomWorkspace","ViewAppointment","ViewAppointmentSlot","ViewMedicalRecord","ViewOrder","ViewOrganization","ViewOrganizationMember","ViewPatient","ViewPreferredProvider","ViewReferral","ViewReferralHistory","ViewTag"],"CacheId":"1f61822b-0b4c-4162-82e8-c8a711d92c13","AcceptedPolicyIds":[],"LoginError":[]}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:26:05.7416700Z</x:t>
   </x:si>
   <x:si>
     <x:t>UserName</x:t>
@@ -217,13 +217,13 @@
     <x:t>hospital@rovicare.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-03T13:41:43.7328024Z</x:t>
+    <x:t>2026-08-08T10:26:05.7592720Z</x:t>
   </x:si>
   <x:si>
     <x:t>EmailId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-03T13:41:43.7496754Z</x:t>
+    <x:t>2026-08-08T10:26:05.7670069Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitId</x:t>
@@ -232,13 +232,13 @@
     <x:t>677920c1-831f-11ea-bd7d-04d9f5ab62dc</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-03T13:41:43.7659226Z</x:t>
+    <x:t>2026-08-08T10:26:05.7743082Z</x:t>
   </x:si>
   <x:si>
     <x:t>CompanyBusinessUnitId</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-03T13:41:43.7849097Z</x:t>
+    <x:t>2026-08-08T10:26:05.7805832Z</x:t>
   </x:si>
   <x:si>
     <x:t>BusinessUnitMemberId</x:t>
@@ -247,13 +247,169 @@
     <x:t>5b1a54d8-fd19-49f8-bb2e-fce04aa8b79e</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-03T13:41:43.8007394Z</x:t>
+    <x:t>2026-08-08T10:26:05.7892878Z</x:t>
   </x:si>
   <x:si>
     <x:t>{"BusinessUnitId":"677920c1-831f-11ea-bd7d-04d9f5ab62dc","ParentBusinessUnitId":null,"CompanyType":"Not-for-Profit Corporation","OpenToNonContractedProvider":false,"Name":"Arizona State Hospital","Status":true,"Description":"Provide need &amp; clean environment Provide need ","LocationType":"ABHC/ACT","IsHeadOffice":null,"Latitude":"33.4297","Longitude":"-112.347611","BusinessUnitType":"Pacf","CreatedBy":null,"CreatedOn":null,"LastUpdatedBy":"fb715f93-8322-11ea-bd7d-04d9f5ab62dc","LastUpdatedOn":"2026-08-03T13:37:48.018548","WorkNumber":"2555555555","EmailId":"testingarizona@yopmail.com","Fax":"8069056421","BusinessUnitCategoryType":["Health Plan","Seriously Mentally Ill","care 1","DME Supplier","Telemedicine/Telehealth","Hospice","Mental Health","Home Health","Skilled Nursing(SNF)","ProviderTypeTest01","Residential Treatment Center","Transitional Housing","Outpatient Mental Health Services","DME Supplier","Transportation","Imaging Center","Psychiatry Providers","Behavioral Health Residential Facility","Attendant Care Provider","Acute Rehab","Social Determinants Of Health","Hospital Inpatient","Active Duty Military","Assistance With Activities Of Daily Living","Substance Use","Doctors And Clinicians","DME Provider","Emergency Mental Health Services"],"BusinessUnitAttributes":[{"EntityName":"AhcccsId","EntityValue":""}]}</x:t>
   </x:si>
   <x:si>
     <x:t>2026-08-03T13:44:17.9801146Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{"IsAvailableUserEmail":true,"MemberId":null,"IsSameBusinessUnitMemebr":false}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:53.1870833Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsAvailableUserEmail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>True</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:53.1937220Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsSameBusinessUnitMemebr</x:t>
+  </x:si>
+  <x:si>
+    <x:t>False</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:53.2000955Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[{"SerialNumber":"1","FirstName":"Sample","MiddleName":"Test","LastName":"Member","Email":"sampletestmember@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"2222222222"},{"SerialNumber":"2","FirstName":"friend","MiddleName":"Test","LastName":"LN","Email":"LN1@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"2222222222"},{"SerialNumber":"3","FirstName":"friend23","MiddleName":"Test1","LastName":"LN1","Email":"LN2@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111111111","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"2222222222"},{"SerialNumber":"4","FirstName":"friend26","MiddleName":"Test2r","LastName":"LN2","Email":"LN1@rovicare.com","RoleName":"Case Manager","Designation":"CEO","MobileNumber":"3333333333","WorkNumber":"1111112221","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Email already registered.","FaxNumber":"32323333333"},{"SerialNumber":"5","FirstName":"Aarav","MiddleName":"Kumar","LastName":"Sharma","Email":"aarav.sharma@testmail.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"4000000003","WorkNumber":"4000000001","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"4000000002"},{"SerialNumber":"6","FirstName":"Aarav5","MiddleName":"Test","LastName":"LN5","Email":"user5@rovicare.com","RoleName":"Case Manager","Designation":"Clinical Manager","MobileNumber":"7200000005","WorkNumber":"7000000005","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000005"},{"SerialNumber":"7","FirstName":"Aarav6","MiddleName":"Test","LastName":"LN6","Email":"user6@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000006","WorkNumber":"7000000006","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000006"},{"SerialNumber":"8","FirstName":"Aarav7","MiddleName":"Test","LastName":"LN7","Email":"user7@rovicare.com","RoleName":"Organization Admin","Designation":"Office Manager","MobileNumber":"7200000007","WorkNumber":"7000000007","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000007"},{"SerialNumber":"9","FirstName":"Aarav8","MiddleName":"Test","LastName":"LN8","Email":"user8@rovicare.com","RoleName":"Case Manager","Designation":"Engineer","MobileNumber":"7200000008","WorkNumber":"7000000008","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000008"},{"SerialNumber":"10","FirstName":"Aarav9","MiddleName":"Test","LastName":"LN9","Email":"user9@rovicare.com","RoleName":"TestAdmin@1","Designation":"CEO","MobileNumber":"7200000009","WorkNumber":"7000000009","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000009"},{"SerialNumber":"11","FirstName":"Aarav10","MiddleName":"Test","LastName":"LN10","Email":"user10@rovicare.com","RoleName":"Organization Admin","Designation":"CEO","MobileNumber":"7200000010","WorkNumber":"7000000010","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000010"},{"SerialNumber":"12","FirstName":"Aarav11","MiddleName":"Test","LastName":"LN11","Email":"user11@rovicare.com","RoleName":"Case Manager","Designation":"Team Lead","MobileNumber":"7200000011","WorkNumber":"7000000011","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000011"},{"SerialNumber":"13","FirstName":"Aarav12","MiddleName":"Test","LastName":"LN12","Email":"user12@rovicare.com","RoleName":"TestAdmin@1","Designation":"Office Manager","MobileNumber":"7200000012","WorkNumber":"7000000012","IsPrimaryMember":"Yes","IsSecondaryMember":"No","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000012"},{"SerialNumber":"14","FirstName":"Aarav13","MiddleName":"Test","LastName":"LN13","Email":"user13@rovicare.com","RoleName":"Organization Admin","Designation":"Clinical Manager","MobileNumber":"7200000013","WorkNumber":"7000000013","IsPrimaryMember":"No","IsSecondaryMember":"Yes","MemberId":null,"Status":"Sorry! You already have maximum numbers of members.","FaxNumber":"7100000013"}]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.6961257Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SerialNumber</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7022468Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FirstName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sample</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7079162Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MiddleName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7138732Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LastName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7196449Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RoleName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Organization Admin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7263901Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WorkNumber</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111111111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7322427Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FaxNumber</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2222222222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7379898Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MobileNumber</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3333333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7434019Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsPrimaryMember</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Yes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7491054Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IsSecondaryMember</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7546803Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Email</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sampletestmember@rovicare.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7615611Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CEO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7679123Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Status</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sorry! You already have maximum numbers of members.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7736071Z</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MemberCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-08T10:24:56.7794450Z</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -880,8 +1036,11 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -935,8 +1094,8 @@
     <x:cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </x:cellStyles>
   <x:tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1 1" defaultPivotStyle="PivotStylePreset2_Accent1 1">
-    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{D26516E5-55CF-4383-B99C-4744BEC979F1}"/>
-    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{8889AFAF-0F25-43FB-AD63-19BD239EB8B4}"/>
+    <x:tableStyle name="TableStylePreset3_Accent1 1" pivot="0" count="0" xr9:uid="{0BA3EEB8-F9B2-43F7-AA96-5C4897185480}"/>
+    <x:tableStyle name="PivotStylePreset2_Accent1 1" table="0" count="0" xr9:uid="{595415C5-E8B3-4B06-8AB7-ECCC23E2D1C6}"/>
   </x:tableStyles>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1445,8 +1604,15 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:E3"/>
+  <x:dimension ref="A1:E11"/>
   <x:sheetFormatPr defaultColWidth="8.996339" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26.285714" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="40.142857" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="255" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="29.857143" style="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
@@ -1458,7 +1624,7 @@
       <x:c r="C1" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="D1" s="0" t="s">
+      <x:c r="D1" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
@@ -1470,16 +1636,16 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -1487,46 +1653,46 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
+    </x:row>
+    <x:row r="4" spans="1:5" ht="143" customHeight="1">
+      <x:c r="A4" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:5">
-      <x:c r="A4" s="0" t="s">
+      <x:c r="B4" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="C4" s="0" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="D4" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:5">
+    </x:row>
+    <x:row r="5" spans="1:5" ht="409.5" customHeight="1">
       <x:c r="A5" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D5" s="0" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
@@ -1543,7 +1709,7 @@
       <x:c r="C6" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D6" s="0" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
@@ -1560,7 +1726,7 @@
       <x:c r="C7" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D7" s="0" t="s">
+      <x:c r="D7" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
@@ -1577,7 +1743,7 @@
       <x:c r="C8" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
+      <x:c r="D8" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
@@ -1594,7 +1760,7 @@
       <x:c r="C9" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D9" s="0" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
@@ -1611,14 +1777,14 @@
       <x:c r="C10" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D10" s="0" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>72</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:5">
+    <x:row r="11" spans="1:5" ht="90" customHeight="1">
       <x:c r="A11" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
@@ -1628,11 +1794,317 @@
       <x:c r="C11" s="0" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D11" s="0" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:5">
+      <x:c r="A12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:5">
+      <x:c r="A13" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:5">
+      <x:c r="A14" s="0" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:5">
+      <x:c r="A15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:5">
+      <x:c r="A16" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:5">
+      <x:c r="A17" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:5">
+      <x:c r="A18" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:5">
+      <x:c r="A19" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:5">
+      <x:c r="A20" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:5">
+      <x:c r="A21" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E21" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:5">
+      <x:c r="A22" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E22" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:5">
+      <x:c r="A23" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:5">
+      <x:c r="A24" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:5">
+      <x:c r="A25" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:5">
+      <x:c r="A26" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:5">
+      <x:c r="A27" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:5">
+      <x:c r="A28" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:5">
+      <x:c r="A29" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>126</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
